--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_BUENO ARENAS ALBACETE BASKET.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_BUENO ARENAS ALBACETE BASKET.xlsx
@@ -562,70 +562,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>24.4217</v>
+        <v>27.6494</v>
       </c>
       <c r="E2" t="n">
-        <v>7.370900000000001</v>
+        <v>7.3181</v>
       </c>
       <c r="F2" t="n">
-        <v>17.051</v>
+        <v>20.331</v>
       </c>
       <c r="G2" t="n">
-        <v>18.3922</v>
+        <v>19.4041</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3565</v>
+        <v>1.1284</v>
       </c>
       <c r="I2" t="n">
-        <v>18.0357</v>
+        <v>18.2758</v>
       </c>
       <c r="J2" t="n">
-        <v>16.5128</v>
+        <v>17.3595</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1141000000000001</v>
+        <v>1.4321</v>
       </c>
       <c r="L2" t="n">
-        <v>16.627</v>
+        <v>15.9273</v>
       </c>
       <c r="M2" t="n">
-        <v>1.8792</v>
+        <v>2.0445</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4706999999999999</v>
+        <v>-0.3038</v>
       </c>
       <c r="O2" t="n">
-        <v>1.4088</v>
+        <v>2.3482</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4096999999999998</v>
+        <v>1.8221</v>
       </c>
       <c r="Q2" t="n">
-        <v>-9.013200000000001</v>
+        <v>-9.920299999999999</v>
       </c>
       <c r="R2" t="n">
-        <v>9.4229</v>
+        <v>11.7423</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1229</v>
+        <v>3.9785</v>
       </c>
       <c r="T2" t="n">
-        <v>-5.1229</v>
+        <v>-5.950200000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>8.245799999999999</v>
+        <v>9.928600000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>2.4971</v>
+        <v>2.4449</v>
       </c>
       <c r="W2" t="n">
-        <v>4.9942</v>
+        <v>5.829</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.4971</v>
+        <v>-3.3841</v>
       </c>
     </row>
     <row r="3">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>14.587</v>
+        <v>11.5207</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6584</v>
+        <v>0.6727999999999996</v>
       </c>
       <c r="F3" t="n">
-        <v>8.9285</v>
+        <v>10.8479</v>
       </c>
       <c r="G3" t="n">
-        <v>10.8111</v>
+        <v>9.1846</v>
       </c>
       <c r="H3" t="n">
-        <v>6.4102</v>
+        <v>5.4577</v>
       </c>
       <c r="I3" t="n">
-        <v>4.4008</v>
+        <v>3.727</v>
       </c>
       <c r="J3" t="n">
-        <v>8.915699999999999</v>
+        <v>7.0905</v>
       </c>
       <c r="K3" t="n">
-        <v>4.0432</v>
+        <v>4.0655</v>
       </c>
       <c r="L3" t="n">
-        <v>4.8724</v>
+        <v>3.025</v>
       </c>
       <c r="M3" t="n">
-        <v>1.8953</v>
+        <v>2.0939</v>
       </c>
       <c r="N3" t="n">
-        <v>2.367</v>
+        <v>1.3922</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4714999999999998</v>
+        <v>0.7018</v>
       </c>
       <c r="P3" t="n">
-        <v>5.1212</v>
+        <v>3.2392</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.8921</v>
+        <v>-6.8834</v>
       </c>
       <c r="R3" t="n">
-        <v>9.013400000000001</v>
+        <v>10.1225</v>
       </c>
       <c r="S3" t="n">
-        <v>-4.161</v>
+        <v>-3.8141</v>
       </c>
       <c r="T3" t="n">
-        <v>-3.6332</v>
+        <v>-3.8579</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5277999999999999</v>
+        <v>0.04379999999999995</v>
       </c>
       <c r="V3" t="n">
-        <v>2.8155</v>
+        <v>2.9111</v>
       </c>
       <c r="W3" t="n">
-        <v>4.268000000000001</v>
+        <v>4.323399999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.4525</v>
+        <v>-1.4123</v>
       </c>
     </row>
     <row r="4">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>9.747400000000001</v>
+        <v>8.994400000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>5.063599999999999</v>
+        <v>2.7711</v>
       </c>
       <c r="F4" t="n">
-        <v>4.6839</v>
+        <v>6.2233</v>
       </c>
       <c r="G4" t="n">
-        <v>7.7294</v>
+        <v>3.337799999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6417999999999999</v>
+        <v>-3.9702</v>
       </c>
       <c r="I4" t="n">
-        <v>8.3712</v>
+        <v>7.3079</v>
       </c>
       <c r="J4" t="n">
-        <v>7.4261</v>
+        <v>3.8134</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5077</v>
+        <v>-0.9193000000000002</v>
       </c>
       <c r="L4" t="n">
-        <v>5.9183</v>
+        <v>4.732699999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3033000000000001</v>
+        <v>-0.4755999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.1495</v>
+        <v>-3.0506</v>
       </c>
       <c r="O4" t="n">
-        <v>2.4529</v>
+        <v>2.5753</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8436</v>
+        <v>2.8344</v>
       </c>
       <c r="Q4" t="n">
-        <v>-6.9648</v>
+        <v>-8.098100000000001</v>
       </c>
       <c r="R4" t="n">
-        <v>8.808399999999999</v>
+        <v>10.9325</v>
       </c>
       <c r="S4" t="n">
-        <v>-4.548</v>
+        <v>-4.9142</v>
       </c>
       <c r="T4" t="n">
-        <v>-5.2204</v>
+        <v>-6.101</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6723999999999999</v>
+        <v>1.1869</v>
       </c>
       <c r="V4" t="n">
-        <v>4.7224</v>
+        <v>7.7363</v>
       </c>
       <c r="W4" t="n">
-        <v>9.822800000000001</v>
+        <v>13.1566</v>
       </c>
       <c r="X4" t="n">
-        <v>-5.1004</v>
+        <v>-5.4203</v>
       </c>
     </row>
     <row r="5">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>6.2936</v>
+        <v>8.931000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>6.9238</v>
+        <v>8.9145</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6301000000000001</v>
+        <v>0.01659999999999995</v>
       </c>
       <c r="G5" t="n">
-        <v>4.4698</v>
+        <v>7.1396</v>
       </c>
       <c r="H5" t="n">
-        <v>2.2813</v>
+        <v>4.5811</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1883</v>
+        <v>2.5583</v>
       </c>
       <c r="J5" t="n">
-        <v>5.8614</v>
+        <v>8.336499999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>4.5969</v>
+        <v>6.9452</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2645</v>
+        <v>1.3915</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3916</v>
+        <v>-1.197</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.3154</v>
+        <v>-2.364</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9239000000000001</v>
+        <v>1.1669</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.2534</v>
+        <v>-3.4416</v>
       </c>
       <c r="Q5" t="n">
-        <v>-5.3261</v>
+        <v>-7.4907</v>
       </c>
       <c r="R5" t="n">
-        <v>3.0727</v>
+        <v>4.0491</v>
       </c>
       <c r="S5" t="n">
-        <v>3.6992</v>
+        <v>4.5736</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2267</v>
+        <v>3.5874</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4726</v>
+        <v>0.9862</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3779000000000001</v>
+        <v>0.6595999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>4.1618</v>
+        <v>4.4811</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.7839</v>
+        <v>-3.8215</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. GARCIA BORREGO</t>
+          <t>M. VORONIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>3.5169</v>
+        <v>6.723100000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>4.659</v>
+        <v>0.5625</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1422</v>
+        <v>6.160600000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1027999999999997</v>
+        <v>3.146</v>
       </c>
       <c r="H6" t="n">
-        <v>3.936</v>
+        <v>3.8951</v>
       </c>
       <c r="I6" t="n">
-        <v>-4.0388</v>
+        <v>-0.7492000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9386</v>
+        <v>1.2068</v>
       </c>
       <c r="K6" t="n">
-        <v>7.784400000000001</v>
+        <v>3.0554</v>
       </c>
       <c r="L6" t="n">
-        <v>-3.846</v>
+        <v>-1.8485</v>
       </c>
       <c r="M6" t="n">
-        <v>-4.0412</v>
+        <v>1.9393</v>
       </c>
       <c r="N6" t="n">
-        <v>-3.8485</v>
+        <v>0.8398000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1927999999999999</v>
+        <v>1.0992</v>
       </c>
       <c r="P6" t="n">
-        <v>3.2775</v>
+        <v>7.085799999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.4339</v>
+        <v>-2.632</v>
       </c>
       <c r="R6" t="n">
-        <v>4.7115</v>
+        <v>9.717699999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1745</v>
+        <v>-7.3301</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7021999999999995</v>
+        <v>-4.4652</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4722000000000001</v>
+        <v>-2.8646</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.8324</v>
+        <v>3.8216</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4524</v>
+        <v>6.4529</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.2847</v>
+        <v>-2.6313</v>
       </c>
     </row>
     <row r="7">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>3.1384</v>
+        <v>0.1164999999999998</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.2042</v>
+        <v>-3.8541</v>
       </c>
       <c r="F7" t="n">
-        <v>5.3428</v>
+        <v>3.9705</v>
       </c>
       <c r="G7" t="n">
-        <v>12.3489</v>
+        <v>11.2009</v>
       </c>
       <c r="H7" t="n">
-        <v>6.0849</v>
+        <v>4.9417</v>
       </c>
       <c r="I7" t="n">
-        <v>6.2642</v>
+        <v>6.2593</v>
       </c>
       <c r="J7" t="n">
-        <v>10.6774</v>
+        <v>11.6457</v>
       </c>
       <c r="K7" t="n">
-        <v>5.6139</v>
+        <v>5.3463</v>
       </c>
       <c r="L7" t="n">
-        <v>5.063600000000001</v>
+        <v>6.2994</v>
       </c>
       <c r="M7" t="n">
-        <v>1.6715</v>
+        <v>-0.4449000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4709</v>
+        <v>-0.4046</v>
       </c>
       <c r="O7" t="n">
-        <v>1.2006</v>
+        <v>-0.04019999999999979</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.4339</v>
+        <v>-4.0491</v>
       </c>
       <c r="Q7" t="n">
-        <v>-9.013400000000001</v>
+        <v>-12.147</v>
       </c>
       <c r="R7" t="n">
-        <v>7.5794</v>
+        <v>8.098099999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>-4.5831</v>
+        <v>-4.9992</v>
       </c>
       <c r="T7" t="n">
-        <v>-4.2462</v>
+        <v>-5.2027</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3367</v>
+        <v>0.2032999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>-3.1936</v>
+        <v>-2.0362</v>
       </c>
       <c r="W7" t="n">
-        <v>0.378</v>
+        <v>1.8497</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.5715</v>
+        <v>-3.886</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. VORONIN</t>
+          <t>A. GARCIA BORREGO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>2.2342</v>
+        <v>-0.3463999999999992</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0211</v>
+        <v>2.5429</v>
       </c>
       <c r="F8" t="n">
-        <v>3.255100000000001</v>
+        <v>-2.8893</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8051999999999999</v>
+        <v>-3.7579</v>
       </c>
       <c r="H8" t="n">
-        <v>2.5333</v>
+        <v>0.7106000000000003</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.7282</v>
+        <v>-4.4684</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6031</v>
+        <v>2.6024</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2816</v>
+        <v>5.8027</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.8848</v>
+        <v>-3.2001</v>
       </c>
       <c r="M8" t="n">
-        <v>1.4083</v>
+        <v>-6.360300000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>1.2518</v>
+        <v>-5.091900000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1566</v>
+        <v>-1.2683</v>
       </c>
       <c r="P8" t="n">
-        <v>5.9406</v>
+        <v>4.454</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.6387</v>
+        <v>-1.6197</v>
       </c>
       <c r="R8" t="n">
-        <v>7.579400000000001</v>
+        <v>6.0736</v>
       </c>
       <c r="S8" t="n">
-        <v>-7.1147</v>
+        <v>0.7429999999999997</v>
       </c>
       <c r="T8" t="n">
-        <v>-3.9858</v>
+        <v>0.7427999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-3.1292</v>
+        <v>9.999999999998899e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>2.6032</v>
+        <v>-1.7853</v>
       </c>
       <c r="W8" t="n">
-        <v>5.2065</v>
+        <v>0.8173000000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.6033</v>
+        <v>-2.6025</v>
       </c>
     </row>
     <row r="9">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.8028</v>
+        <v>-2.7883</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.8753</v>
+        <v>-2.8156</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0726</v>
+        <v>0.0273</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.9347</v>
+        <v>-2.9446</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.4168</v>
+        <v>-2.4307</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5179</v>
+        <v>-0.5139</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.3767</v>
+        <v>-2.3533</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.0227</v>
+        <v>-1.0088</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.354</v>
+        <v>-1.3444</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.5913</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3941</v>
+        <v>-1.4218</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8361</v>
+        <v>0.8305</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2535</v>
+        <v>-1.2364</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.655</v>
+        <v>-0.6403</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5985</v>
+        <v>-0.596</v>
       </c>
       <c r="V9" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O. BRAMBLE</t>
+          <t>F. ANDRADE AMIEL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5347</v>
+        <v>-3.2942</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.1199</v>
+        <v>-3.1604</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5851</v>
+        <v>-0.1339000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>3.4888</v>
+        <v>2.8334</v>
       </c>
       <c r="H10" t="n">
-        <v>3.9774</v>
+        <v>0.7309000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4885999999999998</v>
+        <v>2.1026</v>
       </c>
       <c r="J10" t="n">
-        <v>2.4936</v>
+        <v>3.6095</v>
       </c>
       <c r="K10" t="n">
-        <v>3.0032</v>
+        <v>2.603</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5096999999999999</v>
+        <v>1.0066</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9953</v>
+        <v>-0.7760000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>0.9743000000000002</v>
+        <v>-1.8722</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02109999999999995</v>
+        <v>1.096</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.8678</v>
+        <v>-1.0123</v>
       </c>
       <c r="Q10" t="n">
-        <v>-7.1696</v>
+        <v>-5.4663</v>
       </c>
       <c r="R10" t="n">
-        <v>4.3018</v>
+        <v>4.454</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.6266</v>
+        <v>-4.9578</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0954</v>
+        <v>-3.842</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.5314</v>
+        <v>-1.1159</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.5288</v>
+        <v>-0.1575999999999998</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3482</v>
+        <v>2.538</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1806</v>
+        <v>-2.6957</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F. ANDRADE AMIEL</t>
+          <t>O. BRAMBLE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7039</v>
+        <v>-3.4791</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7542</v>
+        <v>-6.157</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9496999999999998</v>
+        <v>2.6777</v>
       </c>
       <c r="G11" t="n">
-        <v>1.7359</v>
+        <v>3.4134</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2814000000000001</v>
+        <v>4.3291</v>
       </c>
       <c r="I11" t="n">
-        <v>2.0174</v>
+        <v>-0.9157999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>2.5219</v>
+        <v>2.514</v>
       </c>
       <c r="K11" t="n">
-        <v>1.6154</v>
+        <v>3.6922</v>
       </c>
       <c r="L11" t="n">
-        <v>0.9064</v>
+        <v>-1.1781</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7859</v>
+        <v>0.8993999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.8968</v>
+        <v>0.6370000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>1.1109</v>
+        <v>0.2622999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4097</v>
+        <v>-2.6319</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.3017</v>
+        <v>-7.0859</v>
       </c>
       <c r="R11" t="n">
-        <v>3.8921</v>
+        <v>4.454</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.5459</v>
+        <v>-2.7265</v>
       </c>
       <c r="T11" t="n">
-        <v>-3.4715</v>
+        <v>-1.2411</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.0747</v>
+        <v>-1.4854</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.4842000000000002</v>
+        <v>-1.5344</v>
       </c>
       <c r="W11" t="n">
-        <v>2.4972</v>
+        <v>-0.3442</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.9813</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="12">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>-12.7204</v>
+        <v>-9.3674</v>
       </c>
       <c r="E12" t="n">
-        <v>-13.4638</v>
+        <v>-10.6073</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7435</v>
+        <v>1.2399</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.286899999999999</v>
+        <v>-5.7587</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6385000000000001</v>
+        <v>-1.5812</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.6483</v>
+        <v>-4.1774</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.893800000000001</v>
+        <v>-4.5756</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.2497</v>
+        <v>-1.5489</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.6443</v>
+        <v>-3.0266</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3930999999999999</v>
+        <v>-1.1831</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6112</v>
+        <v>-0.03239999999999993</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.0042</v>
+        <v>-1.1509</v>
       </c>
       <c r="P12" t="n">
-        <v>0.4095999999999997</v>
+        <v>1.6197</v>
       </c>
       <c r="Q12" t="n">
-        <v>-6.5551</v>
+        <v>-6.4785</v>
       </c>
       <c r="R12" t="n">
-        <v>6.9647</v>
+        <v>8.0982</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.7241</v>
+        <v>-5.8234</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.9216</v>
+        <v>-4.4718</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.8026</v>
+        <v>-1.3515</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.1191</v>
+        <v>0.5951</v>
       </c>
       <c r="W12" t="n">
-        <v>1.9069</v>
+        <v>4.9184</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.0259</v>
+        <v>-4.323399999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>41.17740000000001</v>
+        <v>44.6597</v>
       </c>
       <c r="E13" t="n">
-        <v>1.237199999999998</v>
+        <v>-3.812499999999996</v>
       </c>
       <c r="F13" t="n">
-        <v>39.94049999999999</v>
+        <v>48.4716</v>
       </c>
       <c r="G13" t="n">
-        <v>51.4569</v>
+        <v>47.1986</v>
       </c>
       <c r="H13" t="n">
-        <v>21.6011</v>
+        <v>17.7925</v>
       </c>
       <c r="I13" t="n">
-        <v>29.8558</v>
+        <v>29.40620000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>50.4739</v>
+        <v>51.2494</v>
       </c>
       <c r="K13" t="n">
-        <v>27.0598</v>
+        <v>29.4654</v>
       </c>
       <c r="L13" t="n">
-        <v>23.4134</v>
+        <v>21.7848</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9831000000000001</v>
+        <v>-4.051100000000002</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.458399999999999</v>
+        <v>-11.6723</v>
       </c>
       <c r="O13" t="n">
-        <v>6.442399999999999</v>
+        <v>7.620799999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>10.2422</v>
+        <v>10.1228</v>
       </c>
       <c r="Q13" t="n">
-        <v>-56.33280000000001</v>
+        <v>-68.83420000000001</v>
       </c>
       <c r="R13" t="n">
-        <v>66.5754</v>
+        <v>78.9567</v>
       </c>
       <c r="S13" t="n">
-        <v>-26.5603</v>
+        <v>-26.5066</v>
       </c>
       <c r="T13" t="n">
-        <v>-28.42310000000001</v>
+        <v>-31.442</v>
       </c>
       <c r="U13" t="n">
-        <v>1.8621</v>
+        <v>4.935500000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>6.038600000000001</v>
+        <v>13.8453</v>
       </c>
       <c r="W13" t="n">
-        <v>35.5202</v>
+        <v>45.2124</v>
       </c>
       <c r="X13" t="n">
-        <v>-29.4812</v>
+        <v>-31.3673</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_BUENO ARENAS ALBACETE BASKET.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_BUENO ARENAS ALBACETE BASKET.xlsx
@@ -565,13 +565,13 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>27.6494</v>
+        <v>24.6235</v>
       </c>
       <c r="E2" t="n">
-        <v>7.3181</v>
+        <v>9.155799999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>20.331</v>
+        <v>15.4678</v>
       </c>
       <c r="G2" t="n">
         <v>19.4041</v>
@@ -610,13 +610,13 @@
         <v>11.7423</v>
       </c>
       <c r="S2" t="n">
-        <v>3.9785</v>
+        <v>0.9526000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>-5.950200000000001</v>
+        <v>-4.1128</v>
       </c>
       <c r="U2" t="n">
-        <v>9.928600000000001</v>
+        <v>5.0653</v>
       </c>
       <c r="V2" t="n">
         <v>2.4449</v>
@@ -643,13 +643,13 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>11.5207</v>
+        <v>12.3813</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6727999999999996</v>
+        <v>0.6571999999999996</v>
       </c>
       <c r="F3" t="n">
-        <v>10.8479</v>
+        <v>11.7241</v>
       </c>
       <c r="G3" t="n">
         <v>9.1846</v>
@@ -688,13 +688,13 @@
         <v>10.1225</v>
       </c>
       <c r="S3" t="n">
-        <v>-3.8141</v>
+        <v>-2.9533</v>
       </c>
       <c r="T3" t="n">
-        <v>-3.8579</v>
+        <v>-3.8735</v>
       </c>
       <c r="U3" t="n">
-        <v>0.04379999999999995</v>
+        <v>0.9200999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>2.9111</v>
@@ -721,13 +721,13 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>8.994400000000001</v>
+        <v>11.8583</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7711</v>
+        <v>4.2973</v>
       </c>
       <c r="F4" t="n">
-        <v>6.2233</v>
+        <v>7.5611</v>
       </c>
       <c r="G4" t="n">
         <v>3.337799999999999</v>
@@ -766,13 +766,13 @@
         <v>10.9325</v>
       </c>
       <c r="S4" t="n">
-        <v>-4.9142</v>
+        <v>-2.0501</v>
       </c>
       <c r="T4" t="n">
-        <v>-6.101</v>
+        <v>-4.5748</v>
       </c>
       <c r="U4" t="n">
-        <v>1.1869</v>
+        <v>2.5246</v>
       </c>
       <c r="V4" t="n">
         <v>7.7363</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. VANACLOCHA SANCHEZ</t>
+          <t>M. VORONIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>8.931000000000001</v>
+        <v>10.016</v>
       </c>
       <c r="E5" t="n">
-        <v>8.9145</v>
+        <v>1.3134</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01659999999999995</v>
+        <v>8.702500000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>7.1396</v>
+        <v>3.146</v>
       </c>
       <c r="H5" t="n">
-        <v>4.5811</v>
+        <v>3.8951</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5583</v>
+        <v>-0.7492000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>8.336499999999999</v>
+        <v>1.2068</v>
       </c>
       <c r="K5" t="n">
-        <v>6.9452</v>
+        <v>3.0554</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3915</v>
+        <v>-1.8485</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.197</v>
+        <v>1.9393</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.364</v>
+        <v>0.8398000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>1.1669</v>
+        <v>1.0992</v>
       </c>
       <c r="P5" t="n">
-        <v>-3.4416</v>
+        <v>7.085799999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>-7.4907</v>
+        <v>-2.632</v>
       </c>
       <c r="R5" t="n">
-        <v>4.0491</v>
+        <v>9.717699999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>4.5736</v>
+        <v>-4.0373</v>
       </c>
       <c r="T5" t="n">
-        <v>3.5874</v>
+        <v>-3.7144</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9862</v>
+        <v>-0.3228999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6595999999999999</v>
+        <v>3.8216</v>
       </c>
       <c r="W5" t="n">
-        <v>4.4811</v>
+        <v>6.4529</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.8215</v>
+        <v>-2.6313</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. VORONIN</t>
+          <t>B. VANACLOCHA SANCHEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>6.723100000000001</v>
+        <v>5.900499999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5625</v>
+        <v>5.3936</v>
       </c>
       <c r="F6" t="n">
-        <v>6.160600000000001</v>
+        <v>0.5068999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>3.146</v>
+        <v>7.1396</v>
       </c>
       <c r="H6" t="n">
-        <v>3.8951</v>
+        <v>4.5811</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7492000000000001</v>
+        <v>2.5583</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2068</v>
+        <v>8.336499999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>3.0554</v>
+        <v>6.9452</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.8485</v>
+        <v>1.3915</v>
       </c>
       <c r="M6" t="n">
-        <v>1.9393</v>
+        <v>-1.197</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8398000000000001</v>
+        <v>-2.364</v>
       </c>
       <c r="O6" t="n">
-        <v>1.0992</v>
+        <v>1.1669</v>
       </c>
       <c r="P6" t="n">
-        <v>7.085799999999999</v>
+        <v>-3.4416</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.632</v>
+        <v>-7.4907</v>
       </c>
       <c r="R6" t="n">
-        <v>9.717699999999999</v>
+        <v>4.0491</v>
       </c>
       <c r="S6" t="n">
-        <v>-7.3301</v>
+        <v>1.5431</v>
       </c>
       <c r="T6" t="n">
-        <v>-4.4652</v>
+        <v>0.06649999999999995</v>
       </c>
       <c r="U6" t="n">
-        <v>-2.8646</v>
+        <v>1.4766</v>
       </c>
       <c r="V6" t="n">
-        <v>3.8216</v>
+        <v>0.6595999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>6.4529</v>
+        <v>4.4811</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.6313</v>
+        <v>-3.8215</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1164999999999998</v>
+        <v>2.9283</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.8541</v>
+        <v>-2.6394</v>
       </c>
       <c r="F7" t="n">
-        <v>3.9705</v>
+        <v>5.5678</v>
       </c>
       <c r="G7" t="n">
         <v>11.2009</v>
@@ -1000,13 +1000,13 @@
         <v>8.098099999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>-4.9992</v>
+        <v>-2.1874</v>
       </c>
       <c r="T7" t="n">
-        <v>-5.2027</v>
+        <v>-3.988</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2032999999999999</v>
+        <v>1.8007</v>
       </c>
       <c r="V7" t="n">
         <v>-2.0362</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. GARCIA BORREGO</t>
+          <t>F. ANDRADE AMIEL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3463999999999992</v>
+        <v>-0.5645999999999995</v>
       </c>
       <c r="E8" t="n">
-        <v>2.5429</v>
+        <v>-1.7622</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.8893</v>
+        <v>1.1977</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.7579</v>
+        <v>2.8334</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7106000000000003</v>
+        <v>0.7309000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-4.4684</v>
+        <v>2.1026</v>
       </c>
       <c r="J8" t="n">
-        <v>2.6024</v>
+        <v>3.6095</v>
       </c>
       <c r="K8" t="n">
-        <v>5.8027</v>
+        <v>2.603</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.2001</v>
+        <v>1.0066</v>
       </c>
       <c r="M8" t="n">
-        <v>-6.360300000000001</v>
+        <v>-0.7760000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-5.091900000000001</v>
+        <v>-1.8722</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.2683</v>
+        <v>1.096</v>
       </c>
       <c r="P8" t="n">
+        <v>-1.0123</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-5.4663</v>
+      </c>
+      <c r="R8" t="n">
         <v>4.454</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-1.6197</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6.0736</v>
-      </c>
       <c r="S8" t="n">
-        <v>0.7429999999999997</v>
+        <v>-2.2281</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7427999999999999</v>
+        <v>-2.4437</v>
       </c>
       <c r="U8" t="n">
-        <v>9.999999999998899e-05</v>
+        <v>0.2158</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.7853</v>
+        <v>-0.1575999999999998</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8173000000000001</v>
+        <v>2.538</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.6025</v>
+        <v>-2.6957</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. VERA PICAZO</t>
+          <t>A. GARCIA BORREGO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7883</v>
+        <v>-0.9485000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.8156</v>
+        <v>0.9546000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0273</v>
+        <v>-1.9033</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.9446</v>
+        <v>-3.7579</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.4307</v>
+        <v>0.7106000000000003</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5139</v>
+        <v>-4.4684</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.3533</v>
+        <v>2.6024</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.0088</v>
+        <v>5.8027</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.3444</v>
+        <v>-3.2001</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5913</v>
+        <v>-6.360300000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4218</v>
+        <v>-5.091900000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8305</v>
+        <v>-1.2683</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2025</v>
+        <v>4.454</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0123</v>
+        <v>-1.6197</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2147</v>
+        <v>6.0736</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2364</v>
+        <v>0.1405</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6403</v>
+        <v>-0.8455000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.596</v>
+        <v>0.986</v>
       </c>
       <c r="V9" t="n">
-        <v>1.1902</v>
+        <v>-1.7853</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1902</v>
+        <v>0.8173000000000001</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.6025</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. ANDRADE AMIEL</t>
+          <t>A. VERA PICAZO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2942</v>
+        <v>-2.4764</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1604</v>
+        <v>-2.6478</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1339000000000001</v>
+        <v>0.1714</v>
       </c>
       <c r="G10" t="n">
-        <v>2.8334</v>
+        <v>-2.9446</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7309000000000001</v>
+        <v>-2.4307</v>
       </c>
       <c r="I10" t="n">
-        <v>2.1026</v>
+        <v>-0.5139</v>
       </c>
       <c r="J10" t="n">
-        <v>3.6095</v>
+        <v>-2.3533</v>
       </c>
       <c r="K10" t="n">
-        <v>2.603</v>
+        <v>-1.0088</v>
       </c>
       <c r="L10" t="n">
-        <v>1.0066</v>
+        <v>-1.3444</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7760000000000001</v>
+        <v>-0.5913</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.8722</v>
+        <v>-1.4218</v>
       </c>
       <c r="O10" t="n">
-        <v>1.096</v>
+        <v>0.8305</v>
       </c>
       <c r="P10" t="n">
+        <v>0.2025</v>
+      </c>
+      <c r="Q10" t="n">
         <v>-1.0123</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-5.4663</v>
-      </c>
       <c r="R10" t="n">
-        <v>4.454</v>
+        <v>1.2147</v>
       </c>
       <c r="S10" t="n">
-        <v>-4.9578</v>
+        <v>-0.9244</v>
       </c>
       <c r="T10" t="n">
-        <v>-3.842</v>
+        <v>-0.4725</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1159</v>
+        <v>-0.452</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1575999999999998</v>
+        <v>1.1902</v>
       </c>
       <c r="W10" t="n">
-        <v>2.538</v>
+        <v>1.1902</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.6957</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4791</v>
+        <v>-3.010699999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.157</v>
+        <v>-6.3802</v>
       </c>
       <c r="F11" t="n">
-        <v>2.6777</v>
+        <v>3.3693</v>
       </c>
       <c r="G11" t="n">
         <v>3.4134</v>
@@ -1312,13 +1312,13 @@
         <v>4.454</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.7265</v>
+        <v>-2.2579</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2411</v>
+        <v>-1.4643</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.4854</v>
+        <v>-0.7937</v>
       </c>
       <c r="V11" t="n">
         <v>-1.5344</v>
@@ -1345,13 +1345,13 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.3674</v>
+        <v>-7.63</v>
       </c>
       <c r="E12" t="n">
-        <v>-10.6073</v>
+        <v>-9.273299999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2399</v>
+        <v>1.6434</v>
       </c>
       <c r="G12" t="n">
         <v>-5.7587</v>
@@ -1390,13 +1390,13 @@
         <v>8.0982</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.8234</v>
+        <v>-4.085900000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.4718</v>
+        <v>-3.1379</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.3515</v>
+        <v>-0.9481999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>0.5951</v>
@@ -1423,13 +1423,13 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>44.6597</v>
+        <v>53.0777</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.812499999999996</v>
+        <v>-0.9309999999999992</v>
       </c>
       <c r="F13" t="n">
-        <v>48.4716</v>
+        <v>54.0087</v>
       </c>
       <c r="G13" t="n">
         <v>47.1986</v>
@@ -1450,13 +1450,13 @@
         <v>21.7848</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.051100000000002</v>
+        <v>-4.0511</v>
       </c>
       <c r="N13" t="n">
         <v>-11.6723</v>
       </c>
       <c r="O13" t="n">
-        <v>7.620799999999999</v>
+        <v>7.620800000000001</v>
       </c>
       <c r="P13" t="n">
         <v>10.1228</v>
@@ -1465,22 +1465,22 @@
         <v>-68.83420000000001</v>
       </c>
       <c r="R13" t="n">
-        <v>78.9567</v>
+        <v>78.95669999999998</v>
       </c>
       <c r="S13" t="n">
-        <v>-26.5066</v>
+        <v>-18.0882</v>
       </c>
       <c r="T13" t="n">
-        <v>-31.442</v>
+        <v>-28.5609</v>
       </c>
       <c r="U13" t="n">
-        <v>4.935500000000001</v>
+        <v>10.4723</v>
       </c>
       <c r="V13" t="n">
         <v>13.8453</v>
       </c>
       <c r="W13" t="n">
-        <v>45.2124</v>
+        <v>45.21239999999999</v>
       </c>
       <c r="X13" t="n">
         <v>-31.3673</v>
